--- a/CTEHE2019/Proyectos/EjemploI_2526_Option3_Config1/EjemploI_Option3_Config1.xlsx
+++ b/CTEHE2019/Proyectos/EjemploI_2526_Option3_Config1/EjemploI_Option3_Config1.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ProyectosCTEyCEE\CTEHE2019\Proyectos\EjemploI_2526_Option3_Config1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7EF2575-7111-4AF6-A515-726DD652B8E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F51C5138-9735-4D62-B33D-A3AC3CE1D460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15940" yWindow="80" windowWidth="15860" windowHeight="17240" xr2:uid="{CE833B6C-91C7-4F54-A261-F495565A982B}"/>
+    <workbookView xWindow="15940" yWindow="80" windowWidth="15860" windowHeight="17240" activeTab="1" xr2:uid="{CE833B6C-91C7-4F54-A261-F495565A982B}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Opacos y Huecos" sheetId="1" r:id="rId1"/>
+    <sheet name="PT" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opacos y Huecos'!$A$1:$O$40</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="73">
   <si>
     <t>Ancho ( m)</t>
   </si>
@@ -51,54 +52,6 @@
   </si>
   <si>
     <t>PLANTA BAJA. P02</t>
-  </si>
-  <si>
-    <t>24,00</t>
-  </si>
-  <si>
-    <t>2,20</t>
-  </si>
-  <si>
-    <t>17,40</t>
-  </si>
-  <si>
-    <t>6,60</t>
-  </si>
-  <si>
-    <t>13,00</t>
-  </si>
-  <si>
-    <t>11,00</t>
-  </si>
-  <si>
-    <t>19,60</t>
-  </si>
-  <si>
-    <t>0,22</t>
-  </si>
-  <si>
-    <t>1,14</t>
-  </si>
-  <si>
-    <t>0,37</t>
-  </si>
-  <si>
-    <t>1,80</t>
-  </si>
-  <si>
-    <t>5,70</t>
-  </si>
-  <si>
-    <t>64,00</t>
-  </si>
-  <si>
-    <t>0,00</t>
-  </si>
-  <si>
-    <t>0,19</t>
-  </si>
-  <si>
-    <t>0,59</t>
   </si>
   <si>
     <t>-</t>
@@ -268,207 +221,216 @@
     </r>
   </si>
   <si>
+    <t>TOTALES PLANTA 01</t>
+  </si>
+  <si>
+    <t>NO APLICA</t>
+  </si>
+  <si>
+    <t>M2.N1</t>
+  </si>
+  <si>
+    <t>EXTERIOR</t>
+  </si>
+  <si>
+    <t>H2-N1</t>
+  </si>
+  <si>
+    <t>VENTANA</t>
+  </si>
+  <si>
+    <t>M2.E1</t>
+  </si>
+  <si>
+    <t>H2-E1</t>
+  </si>
+  <si>
+    <t>M2.S1</t>
+  </si>
+  <si>
+    <t>H2-S1</t>
+  </si>
+  <si>
+    <t>M2.O1</t>
+  </si>
+  <si>
+    <t>H2-O1</t>
+  </si>
+  <si>
+    <t>PUERTA</t>
+  </si>
+  <si>
+    <t>H2-O2</t>
+  </si>
+  <si>
+    <t>F2.1</t>
+  </si>
+  <si>
+    <t>NH</t>
+  </si>
+  <si>
+    <t>SUELO</t>
+  </si>
+  <si>
+    <t>F3.1</t>
+  </si>
+  <si>
+    <t>TECHO</t>
+  </si>
+  <si>
+    <t>TOTALES PLANTA 02</t>
+  </si>
+  <si>
+    <t>PLANTA BAJOCUBIERTA. P03</t>
+  </si>
+  <si>
+    <t>H3-N1</t>
+  </si>
+  <si>
+    <t>H3-E1</t>
+  </si>
+  <si>
+    <t>H3-E2</t>
+  </si>
+  <si>
+    <t>H3-S1</t>
+  </si>
+  <si>
+    <t>C3-N1</t>
+  </si>
+  <si>
+    <t>CUBIERTA</t>
+  </si>
+  <si>
+    <t>H3-N2</t>
+  </si>
+  <si>
+    <t>LUCERNARIO</t>
+  </si>
+  <si>
+    <t>C3-E1</t>
+  </si>
+  <si>
+    <t>H3-E3</t>
+  </si>
+  <si>
+    <t>H3-E4</t>
+  </si>
+  <si>
+    <t>C3-S1</t>
+  </si>
+  <si>
+    <t>H3-S2</t>
+  </si>
+  <si>
+    <t>C3-O1</t>
+  </si>
+  <si>
+    <t>TOTALES PLANTA 03</t>
+  </si>
+  <si>
+    <t>TOTALES EDIFICIO</t>
+  </si>
+  <si>
+    <t>Definición</t>
+  </si>
+  <si>
+    <t>Longitud L(m)</t>
+  </si>
+  <si>
+    <t>Jambas</t>
+  </si>
+  <si>
+    <t>Pilares</t>
+  </si>
+  <si>
+    <t>Suelos con terreno</t>
+  </si>
+  <si>
+    <t>P  U  E  N  T  E  S    T  É  R  M  I  C  O  S</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ψ
+T. lineal
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color indexed="9"/>
+        <rFont val="Maiandra GD"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>W/ m·K</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ψ  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color indexed="9"/>
+        <rFont val="Maiandra GD"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>x L W/ K</t>
+    </r>
+  </si>
+  <si>
+    <t>Frente forjados</t>
+  </si>
+  <si>
+    <t>Cubiertas planas</t>
+  </si>
+  <si>
+    <t>Esquinas exteriores</t>
+  </si>
+  <si>
+    <t>Esquinas interiores</t>
+  </si>
+  <si>
+    <t>Forjado int contacto aire</t>
+  </si>
+  <si>
+    <t>Alfeizar</t>
+  </si>
+  <si>
+    <t>Dinteles/capialzados</t>
+  </si>
+  <si>
     <t>PLANTA CÁMARA SANITARIA. P01
-La planta 01 correspondiente al nivel de cámara sanitaria, no se incluye en ninguna de las opciones dentro de la envolvente térmica por lo que no se detallan en la tabla las características de sus cerramientos.</t>
-  </si>
-  <si>
-    <t>TOTALES PLANTA 01</t>
-  </si>
-  <si>
-    <t>0,00             0,00           0,00</t>
-  </si>
-  <si>
-    <t>NO APLICA</t>
-  </si>
-  <si>
-    <t>M2.N1</t>
-  </si>
-  <si>
-    <t>EXTERIOR</t>
-  </si>
-  <si>
-    <t>M, FACHADA</t>
-  </si>
-  <si>
-    <t>H2-N1</t>
-  </si>
-  <si>
-    <t>VENTANA</t>
-  </si>
-  <si>
-    <t>2,2</t>
-  </si>
-  <si>
-    <t>M2.E1</t>
-  </si>
-  <si>
-    <t>H2-E1</t>
-  </si>
-  <si>
-    <t>M2.S1</t>
-  </si>
-  <si>
-    <t>H2-S1</t>
-  </si>
-  <si>
-    <t>M2.O1</t>
-  </si>
-  <si>
-    <t>H2-O1</t>
-  </si>
-  <si>
-    <t>PUERTA</t>
-  </si>
-  <si>
-    <t>H2-O2</t>
-  </si>
-  <si>
-    <t>F2.1</t>
-  </si>
-  <si>
-    <t>NH</t>
-  </si>
-  <si>
-    <t>SUELO</t>
-  </si>
-  <si>
-    <t>F3.1</t>
-  </si>
-  <si>
-    <t>TECHO</t>
-  </si>
-  <si>
-    <t>TOTALES PLANTA 02</t>
-  </si>
-  <si>
-    <t>224,00</t>
-  </si>
-  <si>
-    <t>131,40         28,60        160,00</t>
-  </si>
-  <si>
-    <t>PLANTA BAJOCUBIERTA. P03</t>
-  </si>
-  <si>
-    <t>1,5</t>
-  </si>
-  <si>
-    <t>12,00</t>
-  </si>
-  <si>
-    <t>10,50</t>
-  </si>
-  <si>
-    <t>H3-N1</t>
-  </si>
-  <si>
-    <t>1,50</t>
-  </si>
-  <si>
-    <t>1,29</t>
-  </si>
-  <si>
-    <t>9,00</t>
-  </si>
-  <si>
-    <t>H3-E1</t>
-  </si>
-  <si>
-    <t>H3-E2</t>
-  </si>
-  <si>
-    <t>H3-S1</t>
-  </si>
-  <si>
-    <t>C3-N1</t>
-  </si>
-  <si>
-    <t>CUBIERTA</t>
-  </si>
-  <si>
-    <t>5,65</t>
-  </si>
-  <si>
-    <t>22,60</t>
-  </si>
-  <si>
-    <t>21,60</t>
-  </si>
-  <si>
-    <t>0,17</t>
-  </si>
-  <si>
-    <t>0,33</t>
-  </si>
-  <si>
-    <t>H3-N2</t>
-  </si>
-  <si>
-    <t>LUCERNARIO</t>
-  </si>
-  <si>
-    <t>1,00</t>
-  </si>
-  <si>
-    <t>C3-E1</t>
-  </si>
-  <si>
-    <t>20,60</t>
-  </si>
-  <si>
-    <t>H3-E3</t>
-  </si>
-  <si>
-    <t>H3-E4</t>
-  </si>
-  <si>
-    <t>C3-S1</t>
-  </si>
-  <si>
-    <t>H3-S2</t>
-  </si>
-  <si>
-    <t>C3-O1</t>
-  </si>
-  <si>
-    <t>TOTALES PLANTA 03</t>
-  </si>
-  <si>
-    <t>212,40</t>
-  </si>
-  <si>
-    <t>128,40</t>
-  </si>
-  <si>
-    <t>10,00</t>
-  </si>
-  <si>
-    <t>138,40</t>
-  </si>
-  <si>
-    <t>TOTALES EDIFICIO</t>
-  </si>
-  <si>
-    <t>436,40</t>
-  </si>
-  <si>
-    <t>259,80</t>
-  </si>
-  <si>
-    <t>38,60</t>
-  </si>
-  <si>
-    <t>298,40</t>
+La planta 01 correspondiente al nivel de cámara sanitaria. no se incluye en ninguna de las opciones dentro de la envolvente térmica por lo que no se detallan en la tabla las características de sus cerramientos.</t>
+  </si>
+  <si>
+    <t>0.00             0.00           0.00</t>
+  </si>
+  <si>
+    <t>M. FACHADA</t>
+  </si>
+  <si>
+    <t>131.40         28.60        160.00</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -588,13 +550,59 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color indexed="8"/>
+      <name val="Maiandra GD"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color indexed="9"/>
+      <name val="Maiandra GD"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color indexed="9"/>
+      <name val="Arial"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color indexed="9"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color indexed="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -662,8 +670,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1DCDB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -757,144 +777,275 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1227,19 +1378,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3863B7DE-0E91-4AE3-8967-77E1C3A7DC22}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:O40"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:15" ht="26">
       <c r="A1" s="8" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>0</v>
@@ -1251,34 +1401,34 @@
         <v>2</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="J1" s="12" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="N1" s="12" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="O1" s="3"/>
     </row>
-    <row r="2" spans="1:15" hidden="1">
+    <row r="2" spans="1:15">
       <c r="A2" s="14" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="B2" s="14"/>
       <c r="C2" s="14"/>
@@ -1295,32 +1445,32 @@
       <c r="N2" s="14"/>
       <c r="O2" s="14"/>
     </row>
-    <row r="3" spans="1:15" hidden="1">
+    <row r="3" spans="1:15">
       <c r="A3" s="15" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B3" s="15"/>
       <c r="C3" s="15"/>
       <c r="D3" s="15"/>
       <c r="E3" s="15"/>
       <c r="F3" s="15"/>
-      <c r="G3" s="16" t="s">
-        <v>17</v>
+      <c r="G3" s="16">
+        <v>0</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="17" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="J3" s="17"/>
       <c r="K3" s="17"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="16" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="O3" s="3"/>
     </row>
-    <row r="4" spans="1:15" hidden="1">
+    <row r="4" spans="1:15">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
@@ -1339,384 +1489,384 @@
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
     </row>
-    <row r="5" spans="1:15" hidden="1">
-      <c r="A5" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="20">
+    <row r="5" spans="1:15" s="51" customFormat="1" ht="43.5">
+      <c r="A5" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="45" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" s="47"/>
+      <c r="E5" s="46">
         <v>8</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="46">
         <v>3</v>
       </c>
-      <c r="G5" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="H5" s="21">
-        <v>1</v>
-      </c>
-      <c r="I5" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="J5" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="K5" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="M5" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="N5" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="O5" s="3"/>
+      <c r="G5" s="45">
+        <v>24</v>
+      </c>
+      <c r="H5" s="46">
+        <v>1</v>
+      </c>
+      <c r="I5" s="45">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="J5" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="K5" s="45">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="L5" s="45">
+        <v>0.22</v>
+      </c>
+      <c r="M5" s="45">
+        <v>0.37</v>
+      </c>
+      <c r="N5" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="O5" s="50"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="18" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="20">
         <v>3</v>
       </c>
-      <c r="F6" s="19" t="s">
-        <v>42</v>
+      <c r="F6" s="19">
+        <v>2.2000000000000002</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="21">
         <v>1</v>
       </c>
       <c r="I6" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="J6" s="25">
+        <v>6.6</v>
+      </c>
+      <c r="K6" s="26">
+        <v>6.6</v>
+      </c>
+      <c r="L6" s="22">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="M6" s="23">
+        <v>1.8</v>
+      </c>
+      <c r="N6" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="O6" s="3"/>
+    </row>
+    <row r="7" spans="1:15" s="51" customFormat="1" ht="43.5">
+      <c r="A7" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="J6" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="K6" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="L6" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="M6" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="N6" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="O6" s="3"/>
-    </row>
-    <row r="7" spans="1:15" hidden="1">
-      <c r="A7" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="20">
+      <c r="C7" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" s="47"/>
+      <c r="E7" s="46">
         <v>8</v>
       </c>
-      <c r="F7" s="21">
+      <c r="F7" s="46">
         <v>3</v>
       </c>
-      <c r="G7" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="H7" s="21">
-        <v>1</v>
-      </c>
-      <c r="I7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="J7" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="K7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="L7" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="M7" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="N7" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="O7" s="3"/>
+      <c r="G7" s="45">
+        <v>24</v>
+      </c>
+      <c r="H7" s="46">
+        <v>1</v>
+      </c>
+      <c r="I7" s="45">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="J7" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="K7" s="45">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="L7" s="45">
+        <v>0.22</v>
+      </c>
+      <c r="M7" s="45">
+        <v>0.37</v>
+      </c>
+      <c r="N7" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="O7" s="50"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="18" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="20">
         <v>3</v>
       </c>
-      <c r="F8" s="19" t="s">
-        <v>42</v>
+      <c r="F8" s="19">
+        <v>2.2000000000000002</v>
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="21">
         <v>1</v>
       </c>
       <c r="I8" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="19">
+        <v>6.6</v>
+      </c>
+      <c r="K8" s="19">
+        <v>6.6</v>
+      </c>
+      <c r="L8" s="22">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="M8" s="23">
+        <v>1.8</v>
+      </c>
+      <c r="N8" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" s="51" customFormat="1" ht="43.5">
+      <c r="A9" s="45" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="J8" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="K8" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="L8" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="M8" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="N8" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" hidden="1">
-      <c r="A9" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="20">
+      <c r="C9" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="47"/>
+      <c r="E9" s="46">
         <v>8</v>
       </c>
-      <c r="F9" s="21">
+      <c r="F9" s="46">
         <v>3</v>
       </c>
-      <c r="G9" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="H9" s="21">
-        <v>1</v>
-      </c>
-      <c r="I9" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="J9" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="K9" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="L9" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="M9" s="23" t="s">
+      <c r="G9" s="45">
+        <v>24</v>
+      </c>
+      <c r="H9" s="46">
+        <v>1</v>
+      </c>
+      <c r="I9" s="45">
         <v>13</v>
       </c>
-      <c r="N9" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="O9" s="3"/>
+      <c r="J9" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="K9" s="49">
+        <v>13</v>
+      </c>
+      <c r="L9" s="45">
+        <v>0.22</v>
+      </c>
+      <c r="M9" s="45">
+        <v>0.37</v>
+      </c>
+      <c r="N9" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="O9" s="50"/>
     </row>
     <row r="10" spans="1:15" s="37" customFormat="1">
       <c r="A10" s="31" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="B10" s="32" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="34">
         <v>5</v>
       </c>
-      <c r="F10" s="32" t="s">
-        <v>42</v>
+      <c r="F10" s="32">
+        <v>2.2000000000000002</v>
       </c>
       <c r="G10" s="33"/>
       <c r="H10" s="35">
         <v>1</v>
       </c>
       <c r="I10" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="J10" s="32">
+        <v>11</v>
+      </c>
+      <c r="K10" s="32">
+        <v>11</v>
+      </c>
+      <c r="L10" s="32">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="M10" s="32">
+        <v>1.8</v>
+      </c>
+      <c r="N10" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="O10" s="36"/>
+    </row>
+    <row r="11" spans="1:15" s="51" customFormat="1" ht="43.5">
+      <c r="A11" s="45" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="J10" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="K10" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="L10" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="M10" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="N10" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="O10" s="36"/>
-    </row>
-    <row r="11" spans="1:15" hidden="1">
-      <c r="A11" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="20">
+      <c r="C11" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" s="47"/>
+      <c r="E11" s="46">
         <v>8</v>
       </c>
-      <c r="F11" s="21">
+      <c r="F11" s="46">
         <v>3</v>
       </c>
-      <c r="G11" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="H11" s="21">
-        <v>1</v>
-      </c>
-      <c r="I11" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="J11" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="K11" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="L11" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="M11" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="N11" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="O11" s="3"/>
+      <c r="G11" s="45">
+        <v>24</v>
+      </c>
+      <c r="H11" s="46">
+        <v>1</v>
+      </c>
+      <c r="I11" s="45">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="J11" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="K11" s="45">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="L11" s="45">
+        <v>0.22</v>
+      </c>
+      <c r="M11" s="45">
+        <v>0.37</v>
+      </c>
+      <c r="N11" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="O11" s="50"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="18" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="20">
         <v>1</v>
       </c>
-      <c r="F12" s="19" t="s">
-        <v>42</v>
+      <c r="F12" s="19">
+        <v>2.2000000000000002</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="21">
         <v>1</v>
       </c>
       <c r="I12" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="J12" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="J12" s="19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="K12" s="19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="L12" s="22">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="M12" s="23">
+        <v>5.7</v>
+      </c>
+      <c r="N12" s="24" t="s">
         <v>5</v>
-      </c>
-      <c r="K12" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="L12" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="M12" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="N12" s="24" t="s">
-        <v>21</v>
       </c>
       <c r="O12" s="3"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="18" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="20">
         <v>1</v>
       </c>
-      <c r="F13" s="19" t="s">
-        <v>42</v>
+      <c r="F13" s="19">
+        <v>2.2000000000000002</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="21">
         <v>1</v>
       </c>
       <c r="I13" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="J13" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="J13" s="19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="K13" s="19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="L13" s="22">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="M13" s="23">
+        <v>1.8</v>
+      </c>
+      <c r="N13" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="K13" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="L13" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="M13" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="N13" s="24" t="s">
-        <v>21</v>
-      </c>
       <c r="O13" s="3"/>
     </row>
-    <row r="14" spans="1:15" hidden="1">
+    <row r="14" spans="1:15">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -1733,15 +1883,15 @@
       <c r="N14" s="7"/>
       <c r="O14" s="3"/>
     </row>
-    <row r="15" spans="1:15" hidden="1">
+    <row r="15" spans="1:15">
       <c r="A15" s="18" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="D15" s="20">
         <v>8</v>
@@ -1750,39 +1900,39 @@
         <v>8</v>
       </c>
       <c r="F15" s="5"/>
-      <c r="G15" s="19" t="s">
-        <v>16</v>
+      <c r="G15" s="19">
+        <v>64</v>
       </c>
       <c r="H15" s="21">
         <v>1</v>
       </c>
-      <c r="I15" s="19" t="s">
-        <v>16</v>
+      <c r="I15" s="19">
+        <v>64</v>
       </c>
       <c r="J15" s="5"/>
-      <c r="K15" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="L15" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="M15" s="23" t="s">
-        <v>19</v>
+      <c r="K15" s="19">
+        <v>64</v>
+      </c>
+      <c r="L15" s="22">
+        <v>0.19</v>
+      </c>
+      <c r="M15" s="23">
+        <v>0.59</v>
       </c>
       <c r="N15" s="24" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="O15" s="3"/>
     </row>
-    <row r="16" spans="1:15" hidden="1">
+    <row r="16" spans="1:15">
       <c r="A16" s="27" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="D16" s="29">
         <v>8</v>
@@ -1791,59 +1941,58 @@
         <v>8</v>
       </c>
       <c r="F16" s="6"/>
-      <c r="G16" s="28" t="s">
-        <v>16</v>
+      <c r="G16" s="28">
+        <v>64</v>
       </c>
       <c r="H16" s="30">
         <v>0</v>
       </c>
       <c r="I16" s="28" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J16" s="6"/>
-      <c r="K16" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="L16" s="28" t="s">
-        <v>13</v>
+      <c r="K16" s="28">
+        <v>0</v>
+      </c>
+      <c r="L16" s="28">
+        <v>0.37</v>
       </c>
       <c r="M16" s="28" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="N16" s="28" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="O16" s="3"/>
     </row>
-    <row r="17" spans="1:15" hidden="1"/>
-    <row r="18" spans="1:15" hidden="1">
+    <row r="18" spans="1:15">
       <c r="A18" s="15" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="B18" s="15"/>
       <c r="C18" s="15"/>
       <c r="D18" s="15"/>
       <c r="E18" s="15"/>
       <c r="F18" s="15"/>
-      <c r="G18" s="16" t="s">
-        <v>57</v>
+      <c r="G18" s="16">
+        <v>224</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="17" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="J18" s="17"/>
       <c r="K18" s="17"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
       <c r="N18" s="40" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="O18" s="3"/>
     </row>
-    <row r="19" spans="1:15" hidden="1">
+    <row r="19" spans="1:15">
       <c r="A19" s="4" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -1860,359 +2009,359 @@
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
     </row>
-    <row r="20" spans="1:15" hidden="1">
-      <c r="A20" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20" s="5"/>
-      <c r="E20" s="20">
+    <row r="20" spans="1:15" s="51" customFormat="1" ht="43.5">
+      <c r="A20" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="45" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" s="47"/>
+      <c r="E20" s="46">
         <v>8</v>
       </c>
-      <c r="F20" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="G20" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="H20" s="21">
-        <v>1</v>
-      </c>
-      <c r="I20" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="J20" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="K20" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="L20" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="M20" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="N20" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="O20" s="3"/>
+      <c r="F20" s="45">
+        <v>1.5</v>
+      </c>
+      <c r="G20" s="45">
+        <v>12</v>
+      </c>
+      <c r="H20" s="46">
+        <v>1</v>
+      </c>
+      <c r="I20" s="45">
+        <v>10.5</v>
+      </c>
+      <c r="J20" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="K20" s="45">
+        <v>10.5</v>
+      </c>
+      <c r="L20" s="45">
+        <v>0.22</v>
+      </c>
+      <c r="M20" s="45">
+        <v>0.37</v>
+      </c>
+      <c r="N20" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="O20" s="50"/>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="18" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D21" s="20">
         <v>1</v>
       </c>
       <c r="E21" s="5"/>
-      <c r="F21" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="G21" s="26" t="s">
-        <v>64</v>
+      <c r="F21" s="25">
+        <v>1.5</v>
+      </c>
+      <c r="G21" s="26">
+        <v>1.5</v>
       </c>
       <c r="H21" s="21">
         <v>1</v>
       </c>
       <c r="I21" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="J21" s="19">
+        <v>1.5</v>
+      </c>
+      <c r="K21" s="19">
+        <v>1.5</v>
+      </c>
+      <c r="L21" s="22">
+        <v>1.29</v>
+      </c>
+      <c r="M21" s="23">
+        <v>1.8</v>
+      </c>
+      <c r="N21" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="1:15" s="51" customFormat="1" ht="43.5">
+      <c r="A22" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="J21" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="K21" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="L21" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="M21" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="N21" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="1:15" hidden="1">
-      <c r="A22" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="D22" s="5"/>
-      <c r="E22" s="20">
+      <c r="C22" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" s="47"/>
+      <c r="E22" s="46">
         <v>8</v>
       </c>
-      <c r="F22" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="G22" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="H22" s="21">
-        <v>1</v>
-      </c>
-      <c r="I22" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="J22" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="K22" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="L22" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="M22" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="N22" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="O22" s="3"/>
+      <c r="F22" s="45">
+        <v>1.5</v>
+      </c>
+      <c r="G22" s="45">
+        <v>12</v>
+      </c>
+      <c r="H22" s="46">
+        <v>1</v>
+      </c>
+      <c r="I22" s="45">
+        <v>9</v>
+      </c>
+      <c r="J22" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="K22" s="45">
+        <v>9</v>
+      </c>
+      <c r="L22" s="45">
+        <v>0.22</v>
+      </c>
+      <c r="M22" s="45">
+        <v>0.37</v>
+      </c>
+      <c r="N22" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="O22" s="50"/>
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="18" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D23" s="20">
         <v>1</v>
       </c>
       <c r="E23" s="5"/>
-      <c r="F23" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="G23" s="19" t="s">
-        <v>64</v>
+      <c r="F23" s="19">
+        <v>1.5</v>
+      </c>
+      <c r="G23" s="19">
+        <v>1.5</v>
       </c>
       <c r="H23" s="21">
         <v>1</v>
       </c>
       <c r="I23" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="J23" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="K23" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="L23" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="M23" s="23" t="s">
-        <v>14</v>
+        <v>4</v>
+      </c>
+      <c r="J23" s="19">
+        <v>1.5</v>
+      </c>
+      <c r="K23" s="19">
+        <v>1.5</v>
+      </c>
+      <c r="L23" s="22">
+        <v>1.29</v>
+      </c>
+      <c r="M23" s="23">
+        <v>1.8</v>
       </c>
       <c r="N23" s="24" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="O23" s="3"/>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="18" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D24" s="20">
         <v>1</v>
       </c>
       <c r="E24" s="5"/>
-      <c r="F24" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="G24" s="19" t="s">
-        <v>64</v>
+      <c r="F24" s="19">
+        <v>1.5</v>
+      </c>
+      <c r="G24" s="19">
+        <v>1.5</v>
       </c>
       <c r="H24" s="21">
         <v>1</v>
       </c>
       <c r="I24" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="19">
+        <v>1.5</v>
+      </c>
+      <c r="K24" s="19">
+        <v>1.5</v>
+      </c>
+      <c r="L24" s="22">
+        <v>1.29</v>
+      </c>
+      <c r="M24" s="23">
+        <v>1.8</v>
+      </c>
+      <c r="N24" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="1:15" s="51" customFormat="1" ht="43.5">
+      <c r="A25" s="45" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="J24" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="K24" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="L24" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="M24" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="N24" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="1:15" hidden="1">
-      <c r="A25" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="D25" s="5"/>
-      <c r="E25" s="20">
+      <c r="C25" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="D25" s="47"/>
+      <c r="E25" s="46">
         <v>8</v>
       </c>
-      <c r="F25" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="G25" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="H25" s="21">
-        <v>1</v>
-      </c>
-      <c r="I25" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="J25" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="K25" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="L25" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="M25" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="N25" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="O25" s="3"/>
+      <c r="F25" s="48">
+        <v>1.5</v>
+      </c>
+      <c r="G25" s="49">
+        <v>12</v>
+      </c>
+      <c r="H25" s="46">
+        <v>1</v>
+      </c>
+      <c r="I25" s="45">
+        <v>10.5</v>
+      </c>
+      <c r="J25" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="K25" s="45">
+        <v>10.5</v>
+      </c>
+      <c r="L25" s="45">
+        <v>0.22</v>
+      </c>
+      <c r="M25" s="45">
+        <v>0.37</v>
+      </c>
+      <c r="N25" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="O25" s="50"/>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="18" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D26" s="20">
         <v>1</v>
       </c>
       <c r="E26" s="5"/>
-      <c r="F26" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="G26" s="19" t="s">
-        <v>64</v>
+      <c r="F26" s="19">
+        <v>1.5</v>
+      </c>
+      <c r="G26" s="19">
+        <v>1.5</v>
       </c>
       <c r="H26" s="21">
         <v>1</v>
       </c>
       <c r="I26" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="J26" s="19">
+        <v>1.5</v>
+      </c>
+      <c r="K26" s="19">
+        <v>1.5</v>
+      </c>
+      <c r="L26" s="22">
+        <v>1.29</v>
+      </c>
+      <c r="M26" s="23">
+        <v>1.8</v>
+      </c>
+      <c r="N26" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="1:15" s="51" customFormat="1" ht="43.5">
+      <c r="A27" s="45" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="J26" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="K26" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="L26" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="M26" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="N26" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="1:15" hidden="1">
-      <c r="A27" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="B27" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C27" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="D27" s="5"/>
-      <c r="E27" s="20">
+      <c r="C27" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="D27" s="47"/>
+      <c r="E27" s="46">
         <v>8</v>
       </c>
-      <c r="F27" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="G27" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="H27" s="21">
-        <v>1</v>
-      </c>
-      <c r="I27" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="J27" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="K27" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="L27" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="M27" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="N27" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="1:15" hidden="1">
+      <c r="F27" s="45">
+        <v>1.5</v>
+      </c>
+      <c r="G27" s="45">
+        <v>12</v>
+      </c>
+      <c r="H27" s="46">
+        <v>1</v>
+      </c>
+      <c r="I27" s="45">
+        <v>12</v>
+      </c>
+      <c r="J27" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="K27" s="45">
+        <v>12</v>
+      </c>
+      <c r="L27" s="45">
+        <v>0.22</v>
+      </c>
+      <c r="M27" s="45">
+        <v>0.37</v>
+      </c>
+      <c r="N27" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="O27" s="50"/>
+    </row>
+    <row r="28" spans="1:15">
       <c r="A28" s="27" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="B28" s="28" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="D28" s="29">
         <v>8</v>
@@ -2221,84 +2370,84 @@
         <v>8</v>
       </c>
       <c r="F28" s="6"/>
-      <c r="G28" s="28" t="s">
-        <v>16</v>
+      <c r="G28" s="28">
+        <v>64</v>
       </c>
       <c r="H28" s="30">
         <v>0</v>
       </c>
       <c r="I28" s="28" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J28" s="28" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="K28" s="30">
         <v>0</v>
       </c>
-      <c r="L28" s="28" t="s">
-        <v>13</v>
+      <c r="L28" s="28">
+        <v>0.37</v>
       </c>
       <c r="M28" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="N28" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="1:15" s="51" customFormat="1" ht="29">
+      <c r="A29" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="N28" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="1:15" hidden="1">
-      <c r="A29" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="B29" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C29" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="D29" s="20">
+      <c r="C29" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="D29" s="46">
         <v>8</v>
       </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="G29" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="H29" s="21">
-        <v>1</v>
-      </c>
-      <c r="I29" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="J29" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="K29" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="L29" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="M29" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="N29" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="O29" s="3"/>
+      <c r="E29" s="47"/>
+      <c r="F29" s="48">
+        <v>5.65</v>
+      </c>
+      <c r="G29" s="49">
+        <v>22.6</v>
+      </c>
+      <c r="H29" s="46">
+        <v>1</v>
+      </c>
+      <c r="I29" s="45">
+        <v>21.6</v>
+      </c>
+      <c r="J29" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="K29" s="45">
+        <v>21.6</v>
+      </c>
+      <c r="L29" s="45">
+        <v>0.17</v>
+      </c>
+      <c r="M29" s="45">
+        <v>0.33</v>
+      </c>
+      <c r="N29" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="O29" s="50"/>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="18" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="D30" s="20">
         <v>1</v>
@@ -2307,84 +2456,84 @@
         <v>1</v>
       </c>
       <c r="F30" s="5"/>
-      <c r="G30" s="19" t="s">
-        <v>79</v>
+      <c r="G30" s="19">
+        <v>1</v>
       </c>
       <c r="H30" s="21">
         <v>1</v>
       </c>
       <c r="I30" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="J30" s="19">
+        <v>1</v>
+      </c>
+      <c r="K30" s="19">
+        <v>1</v>
+      </c>
+      <c r="L30" s="22">
+        <v>1.29</v>
+      </c>
+      <c r="M30" s="23">
+        <v>1.8</v>
+      </c>
+      <c r="N30" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="1:15" s="51" customFormat="1" ht="29">
+      <c r="A31" s="45" t="s">
+        <v>46</v>
+      </c>
+      <c r="B31" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="J30" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="K30" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="L30" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="M30" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="N30" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="1:15" hidden="1">
-      <c r="A31" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C31" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="D31" s="20">
+      <c r="C31" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="D31" s="46">
         <v>8</v>
       </c>
-      <c r="E31" s="5"/>
-      <c r="F31" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="G31" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="H31" s="21">
-        <v>1</v>
-      </c>
-      <c r="I31" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="J31" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="L31" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="M31" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="N31" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="O31" s="3"/>
+      <c r="E31" s="47"/>
+      <c r="F31" s="48">
+        <v>5.65</v>
+      </c>
+      <c r="G31" s="49">
+        <v>22.6</v>
+      </c>
+      <c r="H31" s="46">
+        <v>1</v>
+      </c>
+      <c r="I31" s="45">
+        <v>20.6</v>
+      </c>
+      <c r="J31" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="K31" s="45">
+        <v>20.6</v>
+      </c>
+      <c r="L31" s="45">
+        <v>0.17</v>
+      </c>
+      <c r="M31" s="45">
+        <v>0.33</v>
+      </c>
+      <c r="N31" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="O31" s="50"/>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="18" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="D32" s="20">
         <v>1</v>
@@ -2393,41 +2542,41 @@
         <v>1</v>
       </c>
       <c r="F32" s="5"/>
-      <c r="G32" s="19" t="s">
-        <v>79</v>
+      <c r="G32" s="19">
+        <v>1</v>
       </c>
       <c r="H32" s="21">
         <v>1</v>
       </c>
       <c r="I32" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="J32" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="K32" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="L32" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="M32" s="23" t="s">
-        <v>14</v>
+        <v>4</v>
+      </c>
+      <c r="J32" s="19">
+        <v>1</v>
+      </c>
+      <c r="K32" s="19">
+        <v>1</v>
+      </c>
+      <c r="L32" s="22">
+        <v>1.29</v>
+      </c>
+      <c r="M32" s="23">
+        <v>1.8</v>
       </c>
       <c r="N32" s="24" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="O32" s="3"/>
     </row>
     <row r="33" spans="1:15">
       <c r="A33" s="18" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="D33" s="20">
         <v>1</v>
@@ -2436,84 +2585,84 @@
         <v>1</v>
       </c>
       <c r="F33" s="5"/>
-      <c r="G33" s="19" t="s">
-        <v>79</v>
+      <c r="G33" s="19">
+        <v>1</v>
       </c>
       <c r="H33" s="21">
         <v>1</v>
       </c>
       <c r="I33" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="J33" s="19">
+        <v>1</v>
+      </c>
+      <c r="K33" s="19">
+        <v>1</v>
+      </c>
+      <c r="L33" s="22">
+        <v>1.29</v>
+      </c>
+      <c r="M33" s="23">
+        <v>1.8</v>
+      </c>
+      <c r="N33" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="1:15" s="51" customFormat="1" ht="29">
+      <c r="A34" s="45" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="J33" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="K33" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="L33" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="M33" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="N33" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="1:15" hidden="1">
-      <c r="A34" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="B34" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C34" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="D34" s="20">
+      <c r="C34" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="D34" s="46">
         <v>8</v>
       </c>
-      <c r="E34" s="5"/>
-      <c r="F34" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="G34" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="H34" s="21">
-        <v>1</v>
-      </c>
-      <c r="I34" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="J34" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="K34" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="L34" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="M34" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="N34" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="O34" s="3"/>
+      <c r="E34" s="47"/>
+      <c r="F34" s="45">
+        <v>5.65</v>
+      </c>
+      <c r="G34" s="45">
+        <v>22.6</v>
+      </c>
+      <c r="H34" s="46">
+        <v>1</v>
+      </c>
+      <c r="I34" s="45">
+        <v>21.6</v>
+      </c>
+      <c r="J34" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="K34" s="45">
+        <v>21.6</v>
+      </c>
+      <c r="L34" s="45">
+        <v>0.17</v>
+      </c>
+      <c r="M34" s="45">
+        <v>0.33</v>
+      </c>
+      <c r="N34" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="O34" s="50"/>
     </row>
     <row r="35" spans="1:15">
       <c r="A35" s="18" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="D35" s="20">
         <v>1</v>
@@ -2522,76 +2671,76 @@
         <v>1</v>
       </c>
       <c r="F35" s="5"/>
-      <c r="G35" s="19" t="s">
-        <v>79</v>
+      <c r="G35" s="19">
+        <v>1</v>
       </c>
       <c r="H35" s="21">
         <v>1</v>
       </c>
       <c r="I35" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="J35" s="19">
+        <v>1</v>
+      </c>
+      <c r="K35" s="19">
+        <v>1</v>
+      </c>
+      <c r="L35" s="22">
+        <v>1.29</v>
+      </c>
+      <c r="M35" s="23">
+        <v>1.8</v>
+      </c>
+      <c r="N35" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="O35" s="3"/>
+    </row>
+    <row r="36" spans="1:15" s="51" customFormat="1" ht="29">
+      <c r="A36" s="45" t="s">
+        <v>51</v>
+      </c>
+      <c r="B36" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="J35" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="K35" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="L35" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="M35" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="N35" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="36" spans="1:15" hidden="1">
-      <c r="A36" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="B36" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C36" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="D36" s="20">
+      <c r="C36" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="D36" s="46">
         <v>8</v>
       </c>
-      <c r="E36" s="5"/>
-      <c r="F36" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="G36" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="H36" s="21">
-        <v>1</v>
-      </c>
-      <c r="I36" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="J36" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="K36" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="L36" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="M36" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="N36" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="O36" s="3"/>
-    </row>
-    <row r="37" spans="1:15" hidden="1">
+      <c r="E36" s="47"/>
+      <c r="F36" s="45">
+        <v>5.65</v>
+      </c>
+      <c r="G36" s="45">
+        <v>22.6</v>
+      </c>
+      <c r="H36" s="46">
+        <v>1</v>
+      </c>
+      <c r="I36" s="45">
+        <v>22.6</v>
+      </c>
+      <c r="J36" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="K36" s="45">
+        <v>22.6</v>
+      </c>
+      <c r="L36" s="45">
+        <v>0.17</v>
+      </c>
+      <c r="M36" s="45">
+        <v>0.33</v>
+      </c>
+      <c r="N36" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="O36" s="50"/>
+    </row>
+    <row r="37" spans="1:15">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -2608,36 +2757,36 @@
       <c r="N37" s="3"/>
       <c r="O37" s="3"/>
     </row>
-    <row r="38" spans="1:15" hidden="1">
+    <row r="38" spans="1:15">
       <c r="A38" s="15" t="s">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>
       <c r="D38" s="15"/>
       <c r="E38" s="15"/>
       <c r="F38" s="15"/>
-      <c r="G38" s="16" t="s">
-        <v>88</v>
+      <c r="G38" s="16">
+        <v>212.4</v>
       </c>
       <c r="H38" s="1"/>
-      <c r="I38" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="J38" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="K38" s="16" t="s">
-        <v>91</v>
+      <c r="I38" s="16">
+        <v>128.4</v>
+      </c>
+      <c r="J38" s="16">
+        <v>10</v>
+      </c>
+      <c r="K38" s="16">
+        <v>138.4</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
       <c r="N38" s="40" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="O38" s="3"/>
     </row>
-    <row r="39" spans="1:15" hidden="1">
+    <row r="39" spans="1:15">
       <c r="A39" s="41"/>
       <c r="B39" s="41"/>
       <c r="C39" s="41"/>
@@ -2654,45 +2803,37 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
     </row>
-    <row r="40" spans="1:15" hidden="1">
+    <row r="40" spans="1:15">
       <c r="A40" s="42" t="s">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c r="B40" s="42"/>
       <c r="C40" s="42"/>
       <c r="D40" s="42"/>
       <c r="E40" s="42"/>
       <c r="F40" s="42"/>
-      <c r="G40" s="43" t="s">
-        <v>93</v>
+      <c r="G40" s="43">
+        <v>436.4</v>
       </c>
       <c r="H40" s="38"/>
-      <c r="I40" s="43" t="s">
-        <v>94</v>
-      </c>
-      <c r="J40" s="43" t="s">
-        <v>95</v>
-      </c>
-      <c r="K40" s="43" t="s">
-        <v>96</v>
+      <c r="I40" s="43">
+        <v>259.8</v>
+      </c>
+      <c r="J40" s="43">
+        <v>38.6</v>
+      </c>
+      <c r="K40" s="43">
+        <v>298.39999999999998</v>
       </c>
       <c r="L40" s="39"/>
       <c r="M40" s="39"/>
       <c r="N40" s="44" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="O40" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O40" xr:uid="{3863B7DE-0E91-4AE3-8967-77E1C3A7DC22}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="LUCERNARIO"/>
-        <filter val="PUERTA"/>
-        <filter val="VENTANA"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:O40" xr:uid="{3863B7DE-0E91-4AE3-8967-77E1C3A7DC22}"/>
   <mergeCells count="15">
     <mergeCell ref="A19:O19"/>
     <mergeCell ref="A38:F38"/>
@@ -2712,4 +2853,240 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0120040-16A8-4BC4-A026-CE2DA5998771}">
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="8.26953125" customWidth="1"/>
+    <col min="3" max="3" width="5.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="72">
+      <c r="A1" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+    </row>
+    <row r="2" spans="1:5" ht="27">
+      <c r="A2" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="53"/>
+      <c r="C2" s="54" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="56" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="18">
+      <c r="A3" s="63" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="64"/>
+      <c r="C3" s="57">
+        <v>0.1</v>
+      </c>
+      <c r="D3" s="57">
+        <v>32</v>
+      </c>
+      <c r="E3" s="57">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="18">
+      <c r="A4" s="63" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="64"/>
+      <c r="C4" s="57">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="D4" s="57">
+        <v>32</v>
+      </c>
+      <c r="E4" s="57">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="65"/>
+      <c r="B5" s="65"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="18">
+      <c r="A6" s="63" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="64"/>
+      <c r="C6" s="57">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="D6" s="57">
+        <v>40.6</v>
+      </c>
+      <c r="E6" s="57">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="18">
+      <c r="A7" s="66" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="67"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="18">
+      <c r="A8" s="66" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="67"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="63" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" s="64"/>
+      <c r="C9" s="57">
+        <v>0.51</v>
+      </c>
+      <c r="D9" s="57">
+        <v>13</v>
+      </c>
+      <c r="E9" s="57">
+        <v>6.63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="60"/>
+      <c r="B10" s="60"/>
+      <c r="C10" s="57">
+        <v>0.08</v>
+      </c>
+      <c r="D10" s="57">
+        <v>4</v>
+      </c>
+      <c r="E10" s="57">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="18">
+      <c r="A11" s="63" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="64"/>
+      <c r="C11" s="57">
+        <v>0.01</v>
+      </c>
+      <c r="D11" s="57">
+        <v>13</v>
+      </c>
+      <c r="E11" s="57">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="60"/>
+      <c r="B12" s="60"/>
+      <c r="C12" s="57">
+        <v>0.01</v>
+      </c>
+      <c r="D12" s="57">
+        <v>4</v>
+      </c>
+      <c r="E12" s="57">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="63" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="64"/>
+      <c r="C13" s="57">
+        <v>0.02</v>
+      </c>
+      <c r="D13" s="57">
+        <v>22</v>
+      </c>
+      <c r="E13" s="57">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="60"/>
+      <c r="B14" s="60"/>
+      <c r="C14" s="57">
+        <v>0.02</v>
+      </c>
+      <c r="D14" s="57">
+        <v>20</v>
+      </c>
+      <c r="E14" s="57">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="63" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="64"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
+      <c r="E15" s="57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="18">
+      <c r="A16" s="66" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" s="67"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="21">
+      <c r="A17" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="61"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="62">
+        <v>180.6</v>
+      </c>
+      <c r="E17" s="62">
+        <f>SUMPRODUCT(C3:C15,D3:D15)</f>
+        <v>20.105799999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/CTEHE2019/Proyectos/EjemploI_2526_Option3_Config1/EjemploI_Option3_Config1.xlsx
+++ b/CTEHE2019/Proyectos/EjemploI_2526_Option3_Config1/EjemploI_Option3_Config1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ProyectosCTEyCEE\CTEHE2019\Proyectos\EjemploI_2526_Option3_Config1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB27D2C1-D75C-4CDC-8764-0D29EEB4B930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2B25102-D6BF-498F-9CF1-B9208D359DC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11120" yWindow="80" windowWidth="20680" windowHeight="17240" activeTab="2" xr2:uid="{CE833B6C-91C7-4F54-A261-F495565A982B}"/>
+    <workbookView xWindow="21864" yWindow="156" windowWidth="23928" windowHeight="24960" xr2:uid="{CE833B6C-91C7-4F54-A261-F495565A982B}"/>
   </bookViews>
   <sheets>
     <sheet name="Opacos y Huecos" sheetId="1" r:id="rId1"/>
@@ -409,7 +409,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="28">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -602,6 +602,26 @@
       <sz val="9"/>
       <color indexed="9"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <name val="Maiandra GD"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <name val="Maiandra GD"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -857,12 +877,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -951,7 +971,7 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -991,7 +1011,7 @@
     <xf numFmtId="0" fontId="17" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1007,9 +1027,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1019,7 +1036,7 @@
     <xf numFmtId="0" fontId="19" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1068,6 +1085,16 @@
     <xf numFmtId="0" fontId="27" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -1089,6 +1116,72 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>144780</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3073" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43C36540-2142-5C77-2EC7-1D71E9BA3BDA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="3802380" cy="4244340"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1410,14 +1503,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3863B7DE-0E91-4AE3-8967-77E1C3A7DC22}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:O41"/>
-  <sheetFormatPr defaultRowHeight="10.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="10.8"/>
   <cols>
-    <col min="1" max="12" width="8.7265625" style="2"/>
-    <col min="13" max="13" width="8.7265625" style="47"/>
-    <col min="14" max="16384" width="8.7265625" style="2"/>
+    <col min="1" max="12" width="8.77734375" style="2"/>
+    <col min="13" max="13" width="8.77734375" style="76"/>
+    <col min="14" max="16384" width="8.77734375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="55" customFormat="1" ht="73" customHeight="1">
+    <row r="1" spans="1:15" s="54" customFormat="1" ht="73.05" customHeight="1">
       <c r="A1" s="48" t="s">
         <v>6</v>
       </c>
@@ -1454,15 +1547,15 @@
       <c r="L1" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="53" t="s">
+      <c r="M1" s="73" t="s">
         <v>68</v>
       </c>
       <c r="N1" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="O1" s="54"/>
-    </row>
-    <row r="2" spans="1:15" ht="14.5" hidden="1" customHeight="1">
+      <c r="O1" s="53"/>
+    </row>
+    <row r="2" spans="1:15" ht="14.55" hidden="1" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>64</v>
       </c>
@@ -1481,7 +1574,7 @@
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
     </row>
-    <row r="3" spans="1:15" ht="14.5" hidden="1" customHeight="1">
+    <row r="3" spans="1:15" ht="14.55" hidden="1" customHeight="1">
       <c r="A3" s="5" t="s">
         <v>14</v>
       </c>
@@ -1506,7 +1599,7 @@
       </c>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:15" ht="14.5" hidden="1" customHeight="1">
+    <row r="4" spans="1:15" ht="14.55" hidden="1" customHeight="1">
       <c r="A4" s="11" t="s">
         <v>3</v>
       </c>
@@ -1560,7 +1653,7 @@
       <c r="L5" s="13">
         <v>0.22</v>
       </c>
-      <c r="M5" s="16">
+      <c r="M5" s="74">
         <v>0.37</v>
       </c>
       <c r="N5" s="13" t="s">
@@ -1644,7 +1737,7 @@
       <c r="L7" s="13">
         <v>0.22</v>
       </c>
-      <c r="M7" s="16">
+      <c r="M7" s="74">
         <v>0.37</v>
       </c>
       <c r="N7" s="13" t="s">
@@ -1728,7 +1821,7 @@
       <c r="L9" s="13">
         <v>0.22</v>
       </c>
-      <c r="M9" s="16">
+      <c r="M9" s="74">
         <v>0.37</v>
       </c>
       <c r="N9" s="13" t="s">
@@ -1812,7 +1905,7 @@
       <c r="L11" s="13">
         <v>0.22</v>
       </c>
-      <c r="M11" s="16">
+      <c r="M11" s="74">
         <v>0.37</v>
       </c>
       <c r="N11" s="13" t="s">
@@ -1820,7 +1913,7 @@
       </c>
       <c r="O11" s="17"/>
     </row>
-    <row r="12" spans="1:15" hidden="1">
+    <row r="12" spans="1:15">
       <c r="A12" s="19" t="s">
         <v>25</v>
       </c>
@@ -1952,7 +2045,7 @@
       <c r="L15" s="24">
         <v>0.19</v>
       </c>
-      <c r="M15" s="25">
+      <c r="M15" s="75">
         <v>0.59</v>
       </c>
       <c r="N15" s="26" t="s">
@@ -1993,7 +2086,7 @@
       <c r="L16" s="37">
         <v>0.37</v>
       </c>
-      <c r="M16" s="25" t="s">
+      <c r="M16" s="75" t="s">
         <v>4</v>
       </c>
       <c r="N16" s="37" t="s">
@@ -2001,8 +2094,10 @@
       </c>
       <c r="O16" s="1"/>
     </row>
-    <row r="17" spans="1:15" hidden="1"/>
-    <row r="18" spans="1:15" ht="14.5" hidden="1" customHeight="1">
+    <row r="17" spans="1:15" hidden="1">
+      <c r="M17" s="47"/>
+    </row>
+    <row r="18" spans="1:15" ht="14.55" hidden="1" customHeight="1">
       <c r="A18" s="5" t="s">
         <v>33</v>
       </c>
@@ -2027,7 +2122,7 @@
       </c>
       <c r="O18" s="1"/>
     </row>
-    <row r="19" spans="1:15" ht="14.5" hidden="1" customHeight="1">
+    <row r="19" spans="1:15" ht="14.55" hidden="1" customHeight="1">
       <c r="A19" s="11" t="s">
         <v>34</v>
       </c>
@@ -2081,7 +2176,7 @@
       <c r="L20" s="13">
         <v>0.22</v>
       </c>
-      <c r="M20" s="16">
+      <c r="M20" s="74">
         <v>0.37</v>
       </c>
       <c r="N20" s="13" t="s">
@@ -2167,7 +2262,7 @@
       <c r="L22" s="13">
         <v>0.22</v>
       </c>
-      <c r="M22" s="16">
+      <c r="M22" s="74">
         <v>0.37</v>
       </c>
       <c r="N22" s="13" t="s">
@@ -2296,7 +2391,7 @@
       <c r="L25" s="13">
         <v>0.22</v>
       </c>
-      <c r="M25" s="16">
+      <c r="M25" s="74">
         <v>0.37</v>
       </c>
       <c r="N25" s="13" t="s">
@@ -2382,7 +2477,7 @@
       <c r="L27" s="13">
         <v>0.22</v>
       </c>
-      <c r="M27" s="16">
+      <c r="M27" s="74">
         <v>0.37</v>
       </c>
       <c r="N27" s="13" t="s">
@@ -2425,7 +2520,7 @@
       <c r="L28" s="37">
         <v>0.37</v>
       </c>
-      <c r="M28" s="25" t="s">
+      <c r="M28" s="75" t="s">
         <v>4</v>
       </c>
       <c r="N28" s="37" t="s">
@@ -2476,7 +2571,7 @@
       </c>
       <c r="O29" s="17"/>
     </row>
-    <row r="30" spans="1:15" hidden="1">
+    <row r="30" spans="1:15">
       <c r="A30" s="19" t="s">
         <v>41</v>
       </c>
@@ -2562,7 +2657,7 @@
       </c>
       <c r="O31" s="17"/>
     </row>
-    <row r="32" spans="1:15" hidden="1">
+    <row r="32" spans="1:15">
       <c r="A32" s="19" t="s">
         <v>44</v>
       </c>
@@ -2605,7 +2700,7 @@
       </c>
       <c r="O32" s="1"/>
     </row>
-    <row r="33" spans="1:15" hidden="1">
+    <row r="33" spans="1:15">
       <c r="A33" s="19" t="s">
         <v>45</v>
       </c>
@@ -2691,7 +2786,7 @@
       </c>
       <c r="O34" s="17"/>
     </row>
-    <row r="35" spans="1:15" hidden="1">
+    <row r="35" spans="1:15">
       <c r="A35" s="19" t="s">
         <v>47</v>
       </c>
@@ -2794,7 +2889,7 @@
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
     </row>
-    <row r="38" spans="1:15" ht="14.5" hidden="1" customHeight="1">
+    <row r="38" spans="1:15" ht="14.55" hidden="1" customHeight="1">
       <c r="A38" s="5" t="s">
         <v>49</v>
       </c>
@@ -2840,7 +2935,7 @@
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
     </row>
-    <row r="40" spans="1:15" ht="14.5" hidden="1" customHeight="1">
+    <row r="40" spans="1:15" ht="14.55" hidden="1" customHeight="1">
       <c r="A40" s="42" t="s">
         <v>50</v>
       </c>
@@ -2882,6 +2977,8 @@
   <autoFilter ref="A1:O40" xr:uid="{3863B7DE-0E91-4AE3-8967-77E1C3A7DC22}">
     <filterColumn colId="2">
       <filters>
+        <filter val="LUCERNARIO"/>
+        <filter val="PUERTA"/>
         <filter val="VENTANA"/>
       </filters>
     </filterColumn>
@@ -2892,237 +2989,241 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0120040-16A8-4BC4-A026-CE2DA5998771}">
-  <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="12"/>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="8.26953125" style="57" customWidth="1"/>
-    <col min="2" max="2" width="8.7265625" style="57"/>
-    <col min="3" max="3" width="5.54296875" style="57" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.6328125" style="57" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.1796875" style="57" customWidth="1"/>
-    <col min="6" max="16384" width="8.7265625" style="57"/>
+    <col min="1" max="1" width="8.21875" style="56" customWidth="1"/>
+    <col min="2" max="2" width="8.77734375" style="56"/>
+    <col min="3" max="3" width="5.5546875" style="56" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" style="56" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.21875" style="56" customWidth="1"/>
+    <col min="6" max="16384" width="8.77734375" style="56"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="56" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="58" t="s">
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="57" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="59" t="s">
+      <c r="B2" s="57"/>
+      <c r="C2" s="58" t="s">
         <v>71</v>
       </c>
-      <c r="D2" s="60" t="s">
+      <c r="D2" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="E2" s="61" t="s">
+      <c r="E2" s="60" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="62" t="s">
+    <row r="3" spans="1:7">
+      <c r="A3" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64">
+      <c r="B3" s="62"/>
+      <c r="C3" s="63">
         <v>0.1</v>
       </c>
-      <c r="D3" s="64">
+      <c r="D3" s="63">
         <v>32</v>
       </c>
-      <c r="E3" s="64">
+      <c r="E3" s="63">
         <v>3.2</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="62" t="s">
+    <row r="4" spans="1:7">
+      <c r="A4" s="61" t="s">
         <v>58</v>
       </c>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64">
+      <c r="B4" s="62"/>
+      <c r="C4" s="63">
         <v>0.22500000000000001</v>
       </c>
-      <c r="D4" s="64">
+      <c r="D4" s="63">
         <v>32</v>
       </c>
-      <c r="E4" s="64">
+      <c r="E4" s="63">
         <v>7.2</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="65"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="65"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="64">
+    <row r="5" spans="1:7">
+      <c r="A5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="63">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="62" t="s">
+    <row r="6" spans="1:7">
+      <c r="A6" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="63"/>
-      <c r="C6" s="64">
+      <c r="B6" s="62"/>
+      <c r="C6" s="63">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="D6" s="64">
+      <c r="D6" s="63">
         <v>40.6</v>
       </c>
-      <c r="E6" s="64">
+      <c r="E6" s="63">
         <v>1.75</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="67" t="s">
+    <row r="7" spans="1:7">
+      <c r="A7" s="66" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="68"/>
-      <c r="C7" s="69"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="70">
+      <c r="B7" s="67"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="69">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="67" t="s">
+    <row r="8" spans="1:7">
+      <c r="A8" s="66" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="68"/>
-      <c r="C8" s="69"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="70">
+      <c r="B8" s="67"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="69">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="62" t="s">
+    <row r="9" spans="1:7">
+      <c r="A9" s="61" t="s">
         <v>62</v>
       </c>
-      <c r="B9" s="63"/>
-      <c r="C9" s="64">
+      <c r="B9" s="62"/>
+      <c r="C9" s="63">
         <v>0.51</v>
       </c>
-      <c r="D9" s="64">
+      <c r="D9" s="63">
         <v>13</v>
       </c>
-      <c r="E9" s="64">
+      <c r="E9" s="63">
         <v>6.63</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="71"/>
-      <c r="B10" s="71"/>
-      <c r="C10" s="64">
+    <row r="10" spans="1:7">
+      <c r="A10" s="70"/>
+      <c r="B10" s="70"/>
+      <c r="C10" s="63">
         <v>0.08</v>
       </c>
-      <c r="D10" s="64">
-        <v>4</v>
-      </c>
-      <c r="E10" s="64">
+      <c r="D10" s="63">
+        <v>4</v>
+      </c>
+      <c r="E10" s="63">
         <v>0.32</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="62" t="s">
+    <row r="11" spans="1:7">
+      <c r="A11" s="61" t="s">
         <v>63</v>
       </c>
-      <c r="B11" s="63"/>
-      <c r="C11" s="64">
+      <c r="B11" s="62"/>
+      <c r="C11" s="63">
         <v>0.01</v>
       </c>
-      <c r="D11" s="64">
+      <c r="D11" s="63">
         <v>13</v>
       </c>
-      <c r="E11" s="64">
+      <c r="E11" s="63">
         <v>0.13</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="71"/>
-      <c r="B12" s="71"/>
-      <c r="C12" s="64">
+    <row r="12" spans="1:7">
+      <c r="A12" s="70"/>
+      <c r="B12" s="70"/>
+      <c r="C12" s="63">
         <v>0.01</v>
       </c>
-      <c r="D12" s="64">
-        <v>4</v>
-      </c>
-      <c r="E12" s="64">
+      <c r="D12" s="63">
+        <v>4</v>
+      </c>
+      <c r="E12" s="63">
         <v>0.04</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="62" t="s">
+    <row r="13" spans="1:7">
+      <c r="A13" s="61" t="s">
         <v>53</v>
       </c>
-      <c r="B13" s="63"/>
-      <c r="C13" s="64">
+      <c r="B13" s="62"/>
+      <c r="C13" s="63">
         <v>0.02</v>
       </c>
-      <c r="D13" s="64">
+      <c r="D13" s="63">
         <v>22</v>
       </c>
-      <c r="E13" s="64">
+      <c r="E13" s="63">
         <v>0.44</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="71"/>
-      <c r="B14" s="71"/>
-      <c r="C14" s="64">
+    <row r="14" spans="1:7">
+      <c r="A14" s="70"/>
+      <c r="B14" s="70"/>
+      <c r="C14" s="63">
         <v>0.02</v>
       </c>
-      <c r="D14" s="64">
+      <c r="D14" s="63">
         <v>20</v>
       </c>
-      <c r="E14" s="64">
+      <c r="E14" s="63">
         <v>0.4</v>
       </c>
-      <c r="F14" s="57">
+      <c r="F14" s="56">
         <f>SUM(D9:D14)</f>
         <v>76</v>
       </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="62" t="s">
+      <c r="G14" s="56">
+        <f>SUMPRODUCT(D9:D14,E9:E14)/F14</f>
+        <v>1.4078947368421053</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="B15" s="63"/>
-      <c r="C15" s="71"/>
-      <c r="D15" s="71"/>
-      <c r="E15" s="64">
+      <c r="B15" s="62"/>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="63">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="67" t="s">
+    <row r="16" spans="1:7">
+      <c r="A16" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="B16" s="68"/>
-      <c r="C16" s="69"/>
-      <c r="D16" s="69"/>
-      <c r="E16" s="70">
+      <c r="B16" s="67"/>
+      <c r="C16" s="68"/>
+      <c r="D16" s="68"/>
+      <c r="E16" s="69">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="14.5">
-      <c r="A17" s="72" t="s">
+    <row r="17" spans="1:5" ht="15">
+      <c r="A17" s="71" t="s">
         <v>50</v>
       </c>
-      <c r="B17" s="72"/>
-      <c r="C17" s="72"/>
-      <c r="D17" s="73">
+      <c r="B17" s="71"/>
+      <c r="C17" s="71"/>
+      <c r="D17" s="72">
         <v>180.6</v>
       </c>
-      <c r="E17" s="73">
+      <c r="E17" s="72">
         <f>SUMPRODUCT(C3:C15,D3:D15)</f>
         <v>20.105799999999999</v>
       </c>
@@ -3133,11 +3234,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FFAC64D-834D-4085-98E2-388F007C4E6C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FFAC64D-834D-4085-98E2-388F007C4E6C}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>